--- a/Data/Inputs/baseline_inputs.xlsx
+++ b/Data/Inputs/baseline_inputs.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f50a7c5896c0110/Documents/GitHub/S3D_Senior_Design/Data/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="11_2B59D2BFD35050B3619783B24C3088B35299F368" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79EB48BA-5455-4550-9CB0-5F5433B520B3}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="11_2B59D2BFD35050B3619783B24C3088B35299F368" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08372D3D-DAF5-4F66-8EB1-C4A99F62412A}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="MISSION" sheetId="2" r:id="rId2"/>
-    <sheet name="LOAD" sheetId="3" r:id="rId3"/>
+    <sheet name="LOADS" sheetId="3" r:id="rId3"/>
     <sheet name="TEMP_TARGETS" sheetId="4" r:id="rId4"/>
     <sheet name="FLUID" sheetId="5" r:id="rId5"/>
     <sheet name="COLD_PLATE" sheetId="6" r:id="rId6"/>

--- a/Data/Inputs/baseline_inputs.xlsx
+++ b/Data/Inputs/baseline_inputs.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f50a7c5896c0110/Documents/GitHub/S3D_Senior_Design/Data/Inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Documents\GitHub\S3D_Senior_Design\Data\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="11_2B59D2BFD35050B3619783B24C3088B35299F368" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08372D3D-DAF5-4F66-8EB1-C4A99F62412A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="127" yWindow="232" windowWidth="17851" windowHeight="10733" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="MISSION" sheetId="2" r:id="rId2"/>
-    <sheet name="LOADS" sheetId="3" r:id="rId3"/>
-    <sheet name="TEMP_TARGETS" sheetId="4" r:id="rId4"/>
-    <sheet name="FLUID" sheetId="5" r:id="rId5"/>
-    <sheet name="COLD_PLATE" sheetId="6" r:id="rId6"/>
-    <sheet name="LINES_FITTINGS" sheetId="7" r:id="rId7"/>
-    <sheet name="PUMP" sheetId="8" r:id="rId8"/>
-    <sheet name="RADIATOR" sheetId="9" r:id="rId9"/>
-    <sheet name="ACCUMULATOR" sheetId="10" r:id="rId10"/>
+    <sheet name="MISSION" sheetId="2" r:id="rId1"/>
+    <sheet name="LOADS" sheetId="3" r:id="rId2"/>
+    <sheet name="TEMP_TARGETS" sheetId="4" r:id="rId3"/>
+    <sheet name="FLUID" sheetId="5" r:id="rId4"/>
+    <sheet name="COLD_PLATE" sheetId="6" r:id="rId5"/>
+    <sheet name="LINES_FITTINGS" sheetId="7" r:id="rId6"/>
+    <sheet name="PUMP" sheetId="8" r:id="rId7"/>
+    <sheet name="RADIATOR" sheetId="9" r:id="rId8"/>
+    <sheet name="ACCUMULATOR" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -577,57 +576,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5265744-F42C-4A78-8E40-314EA0846672}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ABEFBB-48EE-43B4-9A53-3C8901A319AC}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="D2">
-        <v>150</v>
+        <v>97.6</v>
       </c>
       <c r="E2">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>120</v>
+        <v>0.38</v>
+      </c>
+      <c r="G2">
+        <v>5670</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -636,66 +644,63 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ABEFBB-48EE-43B4-9A53-3C8901A319AC}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D84F4A01-D184-4813-9443-BE1D90E990FC}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="12.06640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
         <v>500</v>
       </c>
-      <c r="D2">
-        <v>97.6</v>
-      </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="G2">
-        <v>5670</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -704,51 +709,48 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D84F4A01-D184-4813-9443-BE1D90E990FC}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="3" max="3" width="12.1015625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D28781-1DE5-4BC7-A244-49F7049E43D0}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -757,48 +759,60 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D28781-1DE5-4BC7-A244-49F7049E43D0}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A877DE-C76D-4598-8F42-D91A8F5C73A3}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
-        <v>25</v>
+      <c r="B2" t="s">
+        <v>33</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>1035</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>3800</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>0.45</v>
+      </c>
+      <c r="G2">
+        <v>-12</v>
+      </c>
+      <c r="H2">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -807,60 +821,78 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A877DE-C76D-4598-8F42-D91A8F5C73A3}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{466BCCEB-741E-4001-B8C2-C9392AD222EA}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>40</v>
+      </c>
+      <c r="I1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C2">
-        <v>1035</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>3800</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>3.5000000000000001E-3</v>
+        <v>120</v>
       </c>
       <c r="F2">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>80</v>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2">
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -869,78 +901,60 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{466BCCEB-741E-4001-B8C2-C9392AD222EA}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DAAFF80-43CB-41B0-B02C-F752D0F3EB42}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
         <v>15</v>
-      </c>
-      <c r="K2">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -949,60 +963,42 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DAAFF80-43CB-41B0-B02C-F752D0F3EB42}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9CBF6C1-0A1E-4D35-A6CF-EAB64B20810B}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>51</v>
+      <c r="B2">
+        <v>0.25</v>
       </c>
       <c r="C2">
-        <v>2.5</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
       </c>
       <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>15</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1011,42 +1007,60 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9CBF6C1-0A1E-4D35-A6CF-EAB64B20810B}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5997C975-47AB-4C58-B417-5786CCBF3F44}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>60</v>
+      </c>
+      <c r="F1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
+        <v>0.85</v>
+      </c>
+      <c r="C2">
+        <v>0.2</v>
+      </c>
+      <c r="D2">
         <v>0.25</v>
       </c>
-      <c r="C2">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>56</v>
-      </c>
       <c r="E2">
-        <v>0.5</v>
+        <v>0.95</v>
+      </c>
+      <c r="F2">
+        <v>1361</v>
+      </c>
+      <c r="G2">
+        <v>200</v>
+      </c>
+      <c r="H2">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -1055,60 +1069,48 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5997C975-47AB-4C58-B417-5786CCBF3F44}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5265744-F42C-4A78-8E40-314EA0846672}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
-        <v>0.85</v>
+      <c r="B2" t="s">
+        <v>69</v>
       </c>
       <c r="C2">
-        <v>0.2</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>0.25</v>
+        <v>150</v>
       </c>
       <c r="E2">
-        <v>0.95</v>
+        <v>400</v>
       </c>
       <c r="F2">
-        <v>1361</v>
-      </c>
-      <c r="G2">
-        <v>200</v>
-      </c>
-      <c r="H2">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Inputs/baseline_inputs.xlsx
+++ b/Data/Inputs/baseline_inputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Documents\GitHub\S3D_Senior_Design\Data\Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f50a7c5896c0110/Documents/GitHub/S3D_Senior_Design/Data/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59672A4D-E47A-48F1-BA53-A366565570DD}"/>
   <bookViews>
-    <workbookView xWindow="127" yWindow="232" windowWidth="17851" windowHeight="10733" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51720" yWindow="-120" windowWidth="25440" windowHeight="15270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MISSION" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="70">
   <si>
     <t>LEO_SSO</t>
   </si>
@@ -578,9 +578,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ABEFBB-48EE-43B4-9A53-3C8901A319AC}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -609,7 +609,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -646,12 +646,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D84F4A01-D184-4813-9443-BE1D90E990FC}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="3" max="3" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.05078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -677,7 +677,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -688,7 +688,7 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -711,9 +711,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D28781-1DE5-4BC7-A244-49F7049E43D0}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -733,7 +733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -761,9 +761,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A877DE-C76D-4598-8F42-D91A8F5C73A3}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -789,7 +789,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -823,9 +823,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{466BCCEB-741E-4001-B8C2-C9392AD222EA}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -860,7 +860,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -903,9 +903,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DAAFF80-43CB-41B0-B02C-F752D0F3EB42}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -931,7 +931,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -964,10 +964,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9CBF6C1-0A1E-4D35-A6CF-EAB64B20810B}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AA2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -983,8 +983,23 @@
       <c r="E1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="W1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -998,6 +1013,21 @@
         <v>56</v>
       </c>
       <c r="E2">
+        <v>0.5</v>
+      </c>
+      <c r="W2" t="s">
+        <v>11</v>
+      </c>
+      <c r="X2">
+        <v>0.25</v>
+      </c>
+      <c r="Y2">
+        <v>15</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA2">
         <v>0.5</v>
       </c>
     </row>
@@ -1009,9 +1039,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5997C975-47AB-4C58-B417-5786CCBF3F44}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1037,7 +1067,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1071,9 +1101,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5265744-F42C-4A78-8E40-314EA0846672}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1093,7 +1123,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>

--- a/Data/Inputs/baseline_inputs.xlsx
+++ b/Data/Inputs/baseline_inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f50a7c5896c0110/Documents/GitHub/S3D_Senior_Design/Data/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59672A4D-E47A-48F1-BA53-A366565570DD}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F21EDAD1-E0CE-45B8-B356-4594FCD16C92}"/>
   <bookViews>
-    <workbookView xWindow="51720" yWindow="-120" windowWidth="25440" windowHeight="15270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MISSION" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="87">
   <si>
     <t>LEO_SSO</t>
   </si>
@@ -238,6 +238,57 @@
   </si>
   <si>
     <t>BLADDER</t>
+  </si>
+  <si>
+    <t>flow_mode</t>
+  </si>
+  <si>
+    <t>parallel</t>
+  </si>
+  <si>
+    <t>n_passes_serpentine</t>
+  </si>
+  <si>
+    <t>flow_split_model</t>
+  </si>
+  <si>
+    <t>ideal</t>
+  </si>
+  <si>
+    <t>maldistribution_factor</t>
+  </si>
+  <si>
+    <t>spreading_model</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>source_w_mm</t>
+  </si>
+  <si>
+    <t>source_l_mm</t>
+  </si>
+  <si>
+    <t>sink_w_mm</t>
+  </si>
+  <si>
+    <t>sink_l_mm</t>
+  </si>
+  <si>
+    <t>source_to_channels_t_mm</t>
+  </si>
+  <si>
+    <t>K_minor_total</t>
+  </si>
+  <si>
+    <t>interface_h_W_m2K</t>
+  </si>
+  <si>
+    <t>interface_area_mm2</t>
+  </si>
+  <si>
+    <t>plate_k_W_mK</t>
   </si>
 </sst>
 </file>
@@ -822,10 +873,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{466BCCEB-741E-4001-B8C2-C9392AD222EA}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -859,8 +910,50 @@
       <c r="K1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S1" t="s">
+        <v>80</v>
+      </c>
+      <c r="T1" t="s">
+        <v>81</v>
+      </c>
+      <c r="U1" t="s">
+        <v>82</v>
+      </c>
+      <c r="V1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W1" t="s">
+        <v>84</v>
+      </c>
+      <c r="X1" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -893,6 +986,48 @@
       </c>
       <c r="K2">
         <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>5000</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Inputs/baseline_inputs.xlsx
+++ b/Data/Inputs/baseline_inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f50a7c5896c0110/Documents/GitHub/S3D_Senior_Design/Data/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F21EDAD1-E0CE-45B8-B356-4594FCD16C92}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA68A084-3E7A-4F96-8653-C7D331B577B0}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MISSION" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="87">
   <si>
     <t>LEO_SSO</t>
   </si>
@@ -1099,10 +1099,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9CBF6C1-0A1E-4D35-A6CF-EAB64B20810B}">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1118,23 +1118,8 @@
       <c r="E1" t="s">
         <v>55</v>
       </c>
-      <c r="W1" t="s">
-        <v>1</v>
-      </c>
-      <c r="X1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1148,21 +1133,6 @@
         <v>56</v>
       </c>
       <c r="E2">
-        <v>0.5</v>
-      </c>
-      <c r="W2" t="s">
-        <v>11</v>
-      </c>
-      <c r="X2">
-        <v>0.25</v>
-      </c>
-      <c r="Y2">
-        <v>15</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA2">
         <v>0.5</v>
       </c>
     </row>

--- a/Data/Inputs/baseline_inputs.xlsx
+++ b/Data/Inputs/baseline_inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f50a7c5896c0110/Documents/GitHub/S3D_Senior_Design/Data/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA68A084-3E7A-4F96-8653-C7D331B577B0}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4820FB91-139A-4304-9373-090DC3B09577}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MISSION" sheetId="2" r:id="rId1"/>
@@ -87,12 +87,6 @@
     <t>Tmin_C</t>
   </si>
   <si>
-    <t>NVIDIA</t>
-  </si>
-  <si>
-    <t>Nvidia Chip (1)</t>
-  </si>
-  <si>
     <t>T_coolant_in_C</t>
   </si>
   <si>
@@ -243,9 +237,6 @@
     <t>flow_mode</t>
   </si>
   <si>
-    <t>parallel</t>
-  </si>
-  <si>
     <t>n_passes_serpentine</t>
   </si>
   <si>
@@ -289,6 +280,15 @@
   </si>
   <si>
     <t>plate_k_W_mK</t>
+  </si>
+  <si>
+    <t>NVIDIA Module</t>
+  </si>
+  <si>
+    <t>GPU(2)</t>
+  </si>
+  <si>
+    <t>serpentine</t>
   </si>
 </sst>
 </file>
@@ -733,25 +733,25 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
@@ -769,19 +769,19 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -792,13 +792,13 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -819,25 +819,25 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -845,7 +845,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>1035</v>
@@ -881,76 +881,76 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
         <v>34</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>36</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>39</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>41</v>
       </c>
-      <c r="J1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" t="s">
-        <v>43</v>
-      </c>
       <c r="L1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N1" t="s">
         <v>70</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>72</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>73</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>75</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
+        <v>77</v>
+      </c>
+      <c r="T1" t="s">
         <v>78</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>79</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>80</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>81</v>
       </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
         <v>82</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>83</v>
-      </c>
-      <c r="W1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -958,28 +958,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>15</v>
@@ -988,19 +988,19 @@
         <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O2">
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2">
         <v>5000</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>60000</v>
       </c>
       <c r="Y2">
         <v>170</v>
@@ -1045,25 +1045,25 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>48</v>
       </c>
-      <c r="F1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" t="s">
-        <v>50</v>
-      </c>
       <c r="H1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1071,16 +1071,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2">
         <v>2.5</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>8</v>
@@ -1107,16 +1107,16 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>53</v>
-      </c>
-      <c r="D1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1127,10 +1127,10 @@
         <v>0.25</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E2">
         <v>0.5</v>
@@ -1151,25 +1151,25 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>61</v>
-      </c>
-      <c r="G1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1177,13 +1177,13 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="C2">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D2">
-        <v>0.25</v>
+        <v>6.5</v>
       </c>
       <c r="E2">
         <v>0.95</v>
@@ -1213,19 +1213,19 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
         <v>64</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>65</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>66</v>
-      </c>
-      <c r="E1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1233,7 +1233,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C2">
         <v>50</v>

--- a/Data/Inputs/baseline_inputs.xlsx
+++ b/Data/Inputs/baseline_inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f50a7c5896c0110/Documents/GitHub/S3D_Senior_Design/Data/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4820FB91-139A-4304-9373-090DC3B09577}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{ECA59D8B-CD16-4594-B9AE-53D72C7F3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3036F577-03A4-4790-BDD9-D6501A5AB59D}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="96">
   <si>
     <t>LEO_SSO</t>
   </si>
@@ -289,6 +289,33 @@
   </si>
   <si>
     <t>serpentine</t>
+  </si>
+  <si>
+    <t>gpu_count</t>
+  </si>
+  <si>
+    <t>gpu_w_mm</t>
+  </si>
+  <si>
+    <t>gpu_l_mm</t>
+  </si>
+  <si>
+    <t>gpu_arrangement</t>
+  </si>
+  <si>
+    <t>edge_margin_mm</t>
+  </si>
+  <si>
+    <t>channel_pitch_mm</t>
+  </si>
+  <si>
+    <t>channels_per_gpu</t>
+  </si>
+  <si>
+    <t>manifold_length_mm</t>
+  </si>
+  <si>
+    <t>side_by_side</t>
   </si>
 </sst>
 </file>
@@ -873,10 +900,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{466BCCEB-741E-4001-B8C2-C9392AD222EA}">
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -884,76 +911,100 @@
         <v>32</v>
       </c>
       <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="D1" t="s">
+      <c r="L1" t="s">
         <v>34</v>
       </c>
-      <c r="E1" t="s">
+      <c r="M1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" t="s">
+      <c r="N1" t="s">
         <v>36</v>
       </c>
-      <c r="G1" t="s">
+      <c r="O1" t="s">
         <v>37</v>
       </c>
-      <c r="H1" t="s">
+      <c r="P1" t="s">
         <v>38</v>
       </c>
-      <c r="I1" t="s">
+      <c r="Q1" t="s">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="R1" t="s">
         <v>40</v>
       </c>
-      <c r="K1" t="s">
+      <c r="S1" t="s">
         <v>41</v>
       </c>
-      <c r="L1" t="s">
+      <c r="T1" t="s">
         <v>68</v>
       </c>
-      <c r="M1" t="s">
+      <c r="U1" t="s">
         <v>69</v>
       </c>
-      <c r="N1" t="s">
+      <c r="V1" t="s">
         <v>70</v>
       </c>
-      <c r="O1" t="s">
+      <c r="W1" t="s">
         <v>72</v>
       </c>
-      <c r="P1" t="s">
+      <c r="X1" t="s">
         <v>73</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Y1" t="s">
         <v>75</v>
       </c>
-      <c r="R1" t="s">
+      <c r="Z1" t="s">
         <v>76</v>
       </c>
-      <c r="S1" t="s">
+      <c r="AA1" t="s">
         <v>77</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AB1" t="s">
         <v>78</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AC1" t="s">
         <v>79</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AD1" t="s">
         <v>80</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AE1" t="s">
         <v>81</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AF1" t="s">
         <v>82</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AG1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -961,72 +1012,96 @@
         <v>42</v>
       </c>
       <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>112</v>
+      </c>
+      <c r="E2">
+        <v>267</v>
+      </c>
+      <c r="F2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>2.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>20</v>
+      </c>
+      <c r="K2">
         <v>4</v>
       </c>
-      <c r="D2">
+      <c r="L2">
         <v>12</v>
       </c>
-      <c r="E2">
+      <c r="M2">
         <v>300</v>
       </c>
-      <c r="F2">
+      <c r="N2">
         <v>1.5</v>
       </c>
-      <c r="G2">
+      <c r="O2">
         <v>3</v>
       </c>
-      <c r="H2">
+      <c r="P2">
         <v>1.5</v>
       </c>
-      <c r="I2">
+      <c r="Q2">
         <v>3</v>
       </c>
-      <c r="J2">
+      <c r="R2">
         <v>15</v>
       </c>
-      <c r="K2">
+      <c r="S2">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
+      <c r="T2" t="s">
         <v>86</v>
       </c>
-      <c r="M2">
+      <c r="U2">
         <v>1</v>
       </c>
-      <c r="N2" t="s">
+      <c r="V2" t="s">
         <v>71</v>
       </c>
-      <c r="O2">
+      <c r="W2">
         <v>1</v>
       </c>
-      <c r="P2" t="s">
+      <c r="X2" t="s">
         <v>74</v>
       </c>
-      <c r="Q2">
+      <c r="Y2">
         <v>0</v>
       </c>
-      <c r="R2">
+      <c r="Z2">
         <v>0</v>
       </c>
-      <c r="S2">
+      <c r="AA2">
         <v>0</v>
       </c>
-      <c r="T2">
+      <c r="AB2">
         <v>0</v>
       </c>
-      <c r="U2">
+      <c r="AC2">
         <v>0</v>
       </c>
-      <c r="V2">
+      <c r="AD2">
         <v>2</v>
       </c>
-      <c r="W2">
+      <c r="AE2">
         <v>5000</v>
       </c>
-      <c r="X2">
+      <c r="AF2">
         <v>60000</v>
       </c>
-      <c r="Y2">
+      <c r="AG2">
         <v>170</v>
       </c>
     </row>
